--- a/Ocelotl_Ex3A_tables.xlsx
+++ b/Ocelotl_Ex3A_tables.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="25" documentId="8_{54042C58-81AF-49DF-B116-5B74E0BBA9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{579D6A25-2AB9-4BC5-8B9D-EA39D7073B46}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2160" yWindow="2160" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{875D5DE2-E0B2-449F-91C3-EE66D4BB15A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{875D5DE2-E0B2-449F-91C3-EE66D4BB15A7}"/>
   </bookViews>
   <sheets>
     <sheet name="customer" sheetId="1" r:id="rId1"/>

--- a/Ocelotl_Ex3A_tables.xlsx
+++ b/Ocelotl_Ex3A_tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/locelotllopez_my_yearupunited_org/Documents/Documents/data_labs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{54042C58-81AF-49DF-B116-5B74E0BBA9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{579D6A25-2AB9-4BC5-8B9D-EA39D7073B46}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{54042C58-81AF-49DF-B116-5B74E0BBA9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDBABF5E-BB9B-46F3-8B77-EA1794A1A2B4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{875D5DE2-E0B2-449F-91C3-EE66D4BB15A7}"/>
   </bookViews>
@@ -98,7 +98,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -117,6 +117,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -130,12 +142,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,7 +495,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B1" t="s">
@@ -490,10 +504,10 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -530,13 +544,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -573,7 +587,7 @@
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C1" t="s">
@@ -599,7 +613,7 @@
       <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>46127</v>
       </c>
     </row>
